--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AC2C07E-35EB-437B-BAC7-FE14A3682857}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69A75C72-9C8F-48F9-9436-A4FB75C76C1F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -801,21 +801,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1155,7 +1155,9 @@
   <dimension ref="B2:AR11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="44" width="1.7109375" customWidth="1"/>
+    <col min="3" max="24" width="1.7109375" customWidth="1"/>
+    <col min="25" max="25" width="3" customWidth="1"/>
+    <col min="26" max="44" width="1.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1213,59 +1215,59 @@
       <c r="C4" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
       <c r="I4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
       <c r="O4" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="64"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="68"/>
       <c r="U4" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="63"/>
-      <c r="Z4" s="63"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
       <c r="AA4" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="69"/>
       <c r="AG4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="AH4" s="65"/>
-      <c r="AI4" s="65"/>
-      <c r="AJ4" s="65"/>
-      <c r="AK4" s="65"/>
-      <c r="AL4" s="65"/>
-      <c r="AM4" s="67" t="s">
+      <c r="AH4" s="63"/>
+      <c r="AI4" s="63"/>
+      <c r="AJ4" s="63"/>
+      <c r="AK4" s="63"/>
+      <c r="AL4" s="63"/>
+      <c r="AM4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="AN4" s="68"/>
-      <c r="AO4" s="68"/>
-      <c r="AP4" s="68"/>
-      <c r="AQ4" s="68"/>
-      <c r="AR4" s="69"/>
+      <c r="AN4" s="65"/>
+      <c r="AO4" s="65"/>
+      <c r="AP4" s="65"/>
+      <c r="AQ4" s="65"/>
+      <c r="AR4" s="66"/>
     </row>
     <row r="5" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -1540,12 +1542,24 @@
       <c r="R10" s="11"/>
       <c r="S10" s="13"/>
       <c r="T10" s="14"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="15"/>
+      <c r="U10" s="10">
+        <v>6</v>
+      </c>
+      <c r="V10" s="11">
+        <v>1</v>
+      </c>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
+      <c r="X10" s="11">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="13">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="15">
+        <v>8</v>
+      </c>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="12"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69A75C72-9C8F-48F9-9436-A4FB75C76C1F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20AB9082-0255-4CAB-9377-7D6BCFE9032B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1157,7 +1157,9 @@
   <cols>
     <col min="3" max="24" width="1.7109375" customWidth="1"/>
     <col min="25" max="25" width="3" customWidth="1"/>
-    <col min="26" max="44" width="1.7109375" customWidth="1"/>
+    <col min="26" max="37" width="1.7109375" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" customWidth="1"/>
+    <col min="39" max="44" width="1.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1460,12 +1462,24 @@
       <c r="AD8" s="11"/>
       <c r="AE8" s="13"/>
       <c r="AF8" s="14"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="20"/>
+      <c r="AG8" s="16">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="17">
+        <v>6</v>
+      </c>
+      <c r="AI8" s="18">
+        <v>6</v>
+      </c>
+      <c r="AJ8" s="17">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="19">
+        <v>8</v>
+      </c>
+      <c r="AL8" s="20">
+        <v>10</v>
+      </c>
       <c r="AM8" s="21"/>
       <c r="AN8" s="22"/>
       <c r="AO8" s="23"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20AB9082-0255-4CAB-9377-7D6BCFE9032B}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00C2CB5-5FA8-4BFD-8F46-95E722BB7243}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1354,10 +1354,18 @@
       </c>
       <c r="Y6" s="13"/>
       <c r="Z6" s="15"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="11"/>
+      <c r="AA6" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="11">
+        <v>3</v>
+      </c>
+      <c r="AC6" s="12">
+        <v>7</v>
+      </c>
+      <c r="AD6" s="11">
+        <v>5</v>
+      </c>
       <c r="AE6" s="13"/>
       <c r="AF6" s="14"/>
       <c r="AG6" s="16"/>
@@ -1497,10 +1505,18 @@
       <c r="F9" s="11"/>
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="11"/>
+      <c r="I9" s="10">
+        <v>3</v>
+      </c>
+      <c r="J9" s="11">
+        <v>6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>5</v>
+      </c>
+      <c r="L9" s="11">
+        <v>7</v>
+      </c>
       <c r="M9" s="13"/>
       <c r="N9" s="14"/>
       <c r="O9" s="10"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00C2CB5-5FA8-4BFD-8F46-95E722BB7243}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646DB660-B646-4E4B-880E-127CBD8D1321}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11235" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -1464,10 +1464,18 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="11"/>
+      <c r="AA8" s="10">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="11">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="11">
+        <v>6</v>
+      </c>
       <c r="AE8" s="13"/>
       <c r="AF8" s="14"/>
       <c r="AG8" s="16">
@@ -1525,10 +1533,18 @@
       <c r="R9" s="11"/>
       <c r="S9" s="13"/>
       <c r="T9" s="14"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="11"/>
+      <c r="U9" s="10">
+        <v>6</v>
+      </c>
+      <c r="V9" s="11">
+        <v>4</v>
+      </c>
+      <c r="W9" s="12">
+        <v>6</v>
+      </c>
+      <c r="X9" s="11">
+        <v>4</v>
+      </c>
       <c r="Y9" s="13"/>
       <c r="Z9" s="15"/>
       <c r="AA9" s="31"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="40" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646DB660-B646-4E4B-880E-127CBD8D1321}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11235" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646DB660-B646-4E4B-880E-127CBD8D1321}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3ADAEFE-DE3A-4226-AF05-278C5637481B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1438,18 +1438,10 @@
       <c r="F8" s="11"/>
       <c r="G8" s="13"/>
       <c r="H8" s="14"/>
-      <c r="I8" s="10">
-        <v>2</v>
-      </c>
-      <c r="J8" s="11">
-        <v>6</v>
-      </c>
-      <c r="K8" s="12">
-        <v>2</v>
-      </c>
-      <c r="L8" s="11">
-        <v>6</v>
-      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="11"/>
       <c r="M8" s="13"/>
       <c r="N8" s="14"/>
       <c r="O8" s="26"/>
@@ -1513,18 +1505,10 @@
       <c r="F9" s="11"/>
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="10">
-        <v>3</v>
-      </c>
-      <c r="J9" s="11">
-        <v>6</v>
-      </c>
-      <c r="K9" s="12">
-        <v>5</v>
-      </c>
-      <c r="L9" s="11">
-        <v>7</v>
-      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="11"/>
       <c r="M9" s="13"/>
       <c r="N9" s="14"/>
       <c r="O9" s="10"/>
@@ -1533,18 +1517,10 @@
       <c r="R9" s="11"/>
       <c r="S9" s="13"/>
       <c r="T9" s="14"/>
-      <c r="U9" s="10">
-        <v>6</v>
-      </c>
-      <c r="V9" s="11">
-        <v>4</v>
-      </c>
-      <c r="W9" s="12">
-        <v>6</v>
-      </c>
-      <c r="X9" s="11">
-        <v>4</v>
-      </c>
+      <c r="U9" s="10"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="11"/>
       <c r="Y9" s="13"/>
       <c r="Z9" s="15"/>
       <c r="AA9" s="31"/>
@@ -1588,24 +1564,12 @@
       <c r="R10" s="11"/>
       <c r="S10" s="13"/>
       <c r="T10" s="14"/>
-      <c r="U10" s="10">
-        <v>6</v>
-      </c>
-      <c r="V10" s="11">
-        <v>1</v>
-      </c>
-      <c r="W10" s="12">
-        <v>4</v>
-      </c>
-      <c r="X10" s="11">
-        <v>6</v>
-      </c>
-      <c r="Y10" s="13">
-        <v>10</v>
-      </c>
-      <c r="Z10" s="15">
-        <v>8</v>
-      </c>
+      <c r="U10" s="10"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="15"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="12"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3ADAEFE-DE3A-4226-AF05-278C5637481B}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121D41D2-79F6-45E3-B32F-1A612CCE1127}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1438,10 +1438,18 @@
       <c r="F8" s="11"/>
       <c r="G8" s="13"/>
       <c r="H8" s="14"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
+      <c r="I8" s="10">
+        <v>2</v>
+      </c>
+      <c r="J8" s="11">
+        <v>6</v>
+      </c>
+      <c r="K8" s="12">
+        <v>2</v>
+      </c>
+      <c r="L8" s="11">
+        <v>6</v>
+      </c>
       <c r="M8" s="13"/>
       <c r="N8" s="14"/>
       <c r="O8" s="26"/>
@@ -1505,10 +1513,18 @@
       <c r="F9" s="11"/>
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="11"/>
+      <c r="I9" s="10">
+        <v>3</v>
+      </c>
+      <c r="J9" s="11">
+        <v>6</v>
+      </c>
+      <c r="K9" s="12">
+        <v>5</v>
+      </c>
+      <c r="L9" s="11">
+        <v>7</v>
+      </c>
       <c r="M9" s="13"/>
       <c r="N9" s="14"/>
       <c r="O9" s="10"/>
@@ -1517,10 +1533,18 @@
       <c r="R9" s="11"/>
       <c r="S9" s="13"/>
       <c r="T9" s="14"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="11"/>
+      <c r="U9" s="10">
+        <v>6</v>
+      </c>
+      <c r="V9" s="11">
+        <v>4</v>
+      </c>
+      <c r="W9" s="12">
+        <v>6</v>
+      </c>
+      <c r="X9" s="11">
+        <v>4</v>
+      </c>
       <c r="Y9" s="13"/>
       <c r="Z9" s="15"/>
       <c r="AA9" s="31"/>
@@ -1564,12 +1588,24 @@
       <c r="R10" s="11"/>
       <c r="S10" s="13"/>
       <c r="T10" s="14"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="15"/>
+      <c r="U10" s="10">
+        <v>6</v>
+      </c>
+      <c r="V10" s="11">
+        <v>1</v>
+      </c>
+      <c r="W10" s="12">
+        <v>4</v>
+      </c>
+      <c r="X10" s="11">
+        <v>6</v>
+      </c>
+      <c r="Y10" s="13">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="15">
+        <v>8</v>
+      </c>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="12"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121D41D2-79F6-45E3-B32F-1A612CCE1127}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1041B1AD-FE42-4CA6-9C34-2289114D605E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1299,10 +1299,18 @@
       <c r="X5" s="11"/>
       <c r="Y5" s="13"/>
       <c r="Z5" s="15"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="11"/>
+      <c r="AA5" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="11">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="12">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="11">
+        <v>2</v>
+      </c>
       <c r="AE5" s="13"/>
       <c r="AF5" s="14"/>
       <c r="AG5" s="16"/>
@@ -1409,10 +1417,18 @@
       <c r="X7" s="6"/>
       <c r="Y7" s="8"/>
       <c r="Z7" s="35"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="11"/>
+      <c r="AA7" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="11">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="11">
+        <v>6</v>
+      </c>
       <c r="AE7" s="13"/>
       <c r="AF7" s="14"/>
       <c r="AG7" s="16"/>
@@ -1507,10 +1523,18 @@
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="11"/>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11">
+        <v>6</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11">
+        <v>6</v>
+      </c>
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
       <c r="I9" s="10">
@@ -1527,10 +1551,18 @@
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="14"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="11"/>
+      <c r="O9" s="10">
+        <v>6</v>
+      </c>
+      <c r="P9" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>6</v>
+      </c>
+      <c r="R9" s="11">
+        <v>4</v>
+      </c>
       <c r="S9" s="13"/>
       <c r="T9" s="14"/>
       <c r="U9" s="10">

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1041B1AD-FE42-4CA6-9C34-2289114D605E}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45B039CA-503E-41C7-830F-F51B0C0662FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1281,10 +1281,18 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="6">
+        <v>2</v>
+      </c>
+      <c r="K5" s="7">
+        <v>6</v>
+      </c>
+      <c r="L5" s="6">
+        <v>2</v>
+      </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9"/>
       <c r="O5" s="10"/>
@@ -1330,10 +1338,18 @@
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="27"/>
+      <c r="C6" s="26">
+        <v>2</v>
+      </c>
+      <c r="D6" s="27">
+        <v>6</v>
+      </c>
+      <c r="E6" s="28">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27">
+        <v>6</v>
+      </c>
       <c r="G6" s="29"/>
       <c r="H6" s="30"/>
       <c r="I6" s="31"/>
@@ -1585,10 +1601,18 @@
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="4"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="38"/>
+      <c r="AG9" s="37">
+        <v>6</v>
+      </c>
+      <c r="AH9" s="38">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="39">
+        <v>6</v>
+      </c>
+      <c r="AJ9" s="38">
+        <v>4</v>
+      </c>
       <c r="AK9" s="40"/>
       <c r="AL9" s="41"/>
       <c r="AM9" s="21"/>
@@ -1638,10 +1662,18 @@
       <c r="Z10" s="15">
         <v>8</v>
       </c>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="11"/>
+      <c r="AA10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="11">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="11">
+        <v>6</v>
+      </c>
       <c r="AE10" s="13"/>
       <c r="AF10" s="14"/>
       <c r="AG10" s="42"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45B039CA-503E-41C7-830F-F51B0C0662FC}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8220104-A430-4571-8142-2F83ECFC8DCF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1155,7 +1155,13 @@
   <dimension ref="B2:AR11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="24" width="1.7109375" customWidth="1"/>
+    <col min="3" max="7" width="1.7109375" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" customWidth="1"/>
+    <col min="9" max="13" width="1.7109375" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" customWidth="1"/>
+    <col min="15" max="18" width="1.7109375" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" customWidth="1"/>
+    <col min="20" max="24" width="1.7109375" customWidth="1"/>
     <col min="25" max="25" width="3" customWidth="1"/>
     <col min="26" max="37" width="1.7109375" customWidth="1"/>
     <col min="38" max="38" width="4.28515625" customWidth="1"/>
@@ -1295,12 +1301,24 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="14"/>
+      <c r="O5" s="10">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>6</v>
+      </c>
+      <c r="R5" s="11">
+        <v>1</v>
+      </c>
+      <c r="S5" s="13">
+        <v>10</v>
+      </c>
+      <c r="T5" s="14">
+        <v>2</v>
+      </c>
       <c r="U5" s="10"/>
       <c r="V5" s="11"/>
       <c r="W5" s="12"/>
@@ -1358,12 +1376,24 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
+      <c r="O6" s="10">
+        <v>4</v>
+      </c>
+      <c r="P6" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>7</v>
+      </c>
+      <c r="R6" s="11">
+        <v>6</v>
+      </c>
+      <c r="S6" s="13">
+        <v>11</v>
+      </c>
+      <c r="T6" s="14">
+        <v>9</v>
+      </c>
       <c r="U6" s="10">
         <v>6</v>
       </c>
@@ -1409,18 +1439,42 @@
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="14"/>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11">
+        <v>6</v>
+      </c>
+      <c r="G7" s="13">
+        <v>2</v>
+      </c>
+      <c r="H7" s="14">
+        <v>10</v>
+      </c>
+      <c r="I7" s="10">
+        <v>6</v>
+      </c>
+      <c r="J7" s="11">
+        <v>4</v>
+      </c>
+      <c r="K7" s="12">
+        <v>6</v>
+      </c>
+      <c r="L7" s="11">
+        <v>7</v>
+      </c>
+      <c r="M7" s="13">
+        <v>9</v>
+      </c>
+      <c r="N7" s="14">
+        <v>11</v>
+      </c>
       <c r="O7" s="31"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8220104-A430-4571-8142-2F83ECFC8DCF}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB28767D-305B-44D3-A9EA-73E6F2F0DAD2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1339,10 +1339,18 @@
       </c>
       <c r="AE5" s="13"/>
       <c r="AF5" s="14"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="17"/>
+      <c r="AG5" s="16">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="17">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="18">
+        <v>6</v>
+      </c>
+      <c r="AJ5" s="17">
+        <v>2</v>
+      </c>
       <c r="AK5" s="19"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="21"/>
@@ -1680,10 +1688,18 @@
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="11"/>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11">
+        <v>6</v>
+      </c>
+      <c r="E10" s="12">
+        <v>2</v>
+      </c>
+      <c r="F10" s="11">
+        <v>6</v>
+      </c>
       <c r="G10" s="13"/>
       <c r="H10" s="14"/>
       <c r="I10" s="10"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB28767D-305B-44D3-A9EA-73E6F2F0DAD2}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F5E8E9-99D2-43CE-ACC1-C84C23AE1FE4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
@@ -1353,10 +1353,18 @@
       </c>
       <c r="AK5" s="19"/>
       <c r="AL5" s="20"/>
-      <c r="AM5" s="21"/>
-      <c r="AN5" s="22"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="22"/>
+      <c r="AM5" s="21">
+        <v>6</v>
+      </c>
+      <c r="AN5" s="22">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="23">
+        <v>6</v>
+      </c>
+      <c r="AP5" s="22">
+        <v>3</v>
+      </c>
       <c r="AQ5" s="24"/>
       <c r="AR5" s="25"/>
     </row>
@@ -1509,10 +1517,18 @@
       </c>
       <c r="AE7" s="13"/>
       <c r="AF7" s="14"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="18"/>
-      <c r="AJ7" s="17"/>
+      <c r="AG7" s="16">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="17">
+        <v>2</v>
+      </c>
+      <c r="AI7" s="18">
+        <v>7</v>
+      </c>
+      <c r="AJ7" s="17">
+        <v>5</v>
+      </c>
       <c r="AK7" s="19"/>
       <c r="AL7" s="20"/>
       <c r="AM7" s="21"/>
@@ -1708,10 +1724,18 @@
       <c r="L10" s="11"/>
       <c r="M10" s="13"/>
       <c r="N10" s="14"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="11"/>
+      <c r="O10" s="10">
+        <v>2</v>
+      </c>
+      <c r="P10" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>5</v>
+      </c>
+      <c r="R10" s="11">
+        <v>7</v>
+      </c>
       <c r="S10" s="13"/>
       <c r="T10" s="14"/>
       <c r="U10" s="10">
@@ -1763,10 +1787,18 @@
       <c r="B11" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="44">
+        <v>2</v>
+      </c>
+      <c r="D11" s="45">
+        <v>6</v>
+      </c>
+      <c r="E11" s="46">
+        <v>3</v>
+      </c>
+      <c r="F11" s="45">
+        <v>6</v>
+      </c>
       <c r="G11" s="47"/>
       <c r="H11" s="48"/>
       <c r="I11" s="44"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F5E8E9-99D2-43CE-ACC1-C84C23AE1FE4}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E851A72-2682-43ED-912C-77B530F04AB1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
+    <workbookView xWindow="15" yWindow="360" windowWidth="28785" windowHeight="15105" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -1319,10 +1319,18 @@
       <c r="T5" s="14">
         <v>2</v>
       </c>
-      <c r="U5" s="10"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="11"/>
+      <c r="U5" s="10">
+        <v>6</v>
+      </c>
+      <c r="V5" s="11">
+        <v>0</v>
+      </c>
+      <c r="W5" s="12">
+        <v>6</v>
+      </c>
+      <c r="X5" s="11">
+        <v>2</v>
+      </c>
       <c r="Y5" s="13"/>
       <c r="Z5" s="15"/>
       <c r="AA5" s="10">
@@ -1444,10 +1452,18 @@
       <c r="AJ6" s="17"/>
       <c r="AK6" s="19"/>
       <c r="AL6" s="20"/>
-      <c r="AM6" s="21"/>
-      <c r="AN6" s="22"/>
-      <c r="AO6" s="23"/>
-      <c r="AP6" s="22"/>
+      <c r="AM6" s="21">
+        <v>6</v>
+      </c>
+      <c r="AN6" s="22">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="23">
+        <v>6</v>
+      </c>
+      <c r="AP6" s="22">
+        <v>3</v>
+      </c>
       <c r="AQ6" s="24"/>
       <c r="AR6" s="25"/>
     </row>
@@ -1542,10 +1558,18 @@
       <c r="B8" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11"/>
+      <c r="C8" s="10">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11">
+        <v>6</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11">
+        <v>6</v>
+      </c>
       <c r="G8" s="13"/>
       <c r="H8" s="14"/>
       <c r="I8" s="10">
@@ -1776,10 +1800,18 @@
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
-      <c r="AM10" s="21"/>
-      <c r="AN10" s="22"/>
-      <c r="AO10" s="23"/>
-      <c r="AP10" s="22"/>
+      <c r="AM10" s="21">
+        <v>6</v>
+      </c>
+      <c r="AN10" s="22">
+        <v>4</v>
+      </c>
+      <c r="AO10" s="23">
+        <v>6</v>
+      </c>
+      <c r="AP10" s="22">
+        <v>4</v>
+      </c>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="34"/>
     </row>
@@ -1801,10 +1833,18 @@
       </c>
       <c r="G11" s="47"/>
       <c r="H11" s="48"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="45"/>
+      <c r="I11" s="44">
+        <v>4</v>
+      </c>
+      <c r="J11" s="45">
+        <v>6</v>
+      </c>
+      <c r="K11" s="46">
+        <v>3</v>
+      </c>
+      <c r="L11" s="45">
+        <v>6</v>
+      </c>
       <c r="M11" s="47"/>
       <c r="N11" s="48"/>
       <c r="O11" s="44"/>
@@ -1825,10 +1865,18 @@
       <c r="AD11" s="45"/>
       <c r="AE11" s="47"/>
       <c r="AF11" s="48"/>
-      <c r="AG11" s="50"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="50"/>
+      <c r="AG11" s="50">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="51">
+        <v>6</v>
+      </c>
+      <c r="AI11" s="52">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="50">
+        <v>6</v>
+      </c>
       <c r="AK11" s="53"/>
       <c r="AL11" s="54"/>
       <c r="AM11" s="55"/>

--- a/btl online.xlsx
+++ b/btl online.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amkp365businessbasic-my.sharepoint.com/personal/jiri_skalsky_amkp_cz/Documents/Plocha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E851A72-2682-43ED-912C-77B530F04AB1}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{80E77452-4901-442C-B107-1EC33722A14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E8C6AB-0A20-42CA-B827-2005F3000035}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="360" windowWidth="28785" windowHeight="15105" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6074E967-F2E2-4C62-A71C-93890E22AB27}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -1163,7 +1163,8 @@
     <col min="19" max="19" width="4.140625" customWidth="1"/>
     <col min="20" max="24" width="1.7109375" customWidth="1"/>
     <col min="25" max="25" width="3" customWidth="1"/>
-    <col min="26" max="37" width="1.7109375" customWidth="1"/>
+    <col min="26" max="36" width="1.7109375" customWidth="1"/>
+    <col min="37" max="37" width="2.85546875" customWidth="1"/>
     <col min="38" max="38" width="4.28515625" customWidth="1"/>
     <col min="39" max="44" width="1.7109375" customWidth="1"/>
   </cols>
@@ -1446,12 +1447,24 @@
       </c>
       <c r="AE6" s="13"/>
       <c r="AF6" s="14"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="18"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="19"/>
-      <c r="AL6" s="20"/>
+      <c r="AG6" s="16">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="17">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="18">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="17">
+        <v>3</v>
+      </c>
+      <c r="AK6" s="19">
+        <v>10</v>
+      </c>
+      <c r="AL6" s="20">
+        <v>3</v>
+      </c>
       <c r="AM6" s="21">
         <v>6</v>
       </c>
@@ -1742,12 +1755,24 @@
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="14"/>
+      <c r="I10" s="10">
+        <v>6</v>
+      </c>
+      <c r="J10" s="11">
+        <v>4</v>
+      </c>
+      <c r="K10" s="12">
+        <v>3</v>
+      </c>
+      <c r="L10" s="11">
+        <v>6</v>
+      </c>
+      <c r="M10" s="13">
+        <v>3</v>
+      </c>
+      <c r="N10" s="14">
+        <v>10</v>
+      </c>
       <c r="O10" s="10">
         <v>2</v>
       </c>
